--- a/informes_data/Tercera FEB/2025-26/playoffs/individual/NP_play_by_play_2512442_1ºAA1ºABFINAL_PROCESSED.xlsx
+++ b/informes_data/Tercera FEB/2025-26/playoffs/individual/NP_play_by_play_2512442_1ºAA1ºABFINAL_PROCESSED.xlsx
@@ -565,67 +565,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.3693</v>
+        <v>6.7689</v>
       </c>
       <c r="E2" t="n">
-        <v>5.0513</v>
+        <v>5.1472</v>
       </c>
       <c r="F2" t="n">
-        <v>2.3179</v>
+        <v>1.6217</v>
       </c>
       <c r="G2" t="n">
-        <v>4.1952</v>
+        <v>4.2417</v>
       </c>
       <c r="H2" t="n">
-        <v>2.1368</v>
+        <v>2.2189</v>
       </c>
       <c r="I2" t="n">
-        <v>2.0584</v>
+        <v>2.0227</v>
       </c>
       <c r="J2" t="n">
-        <v>4.0826</v>
+        <v>4.2363</v>
       </c>
       <c r="K2" t="n">
-        <v>2.7228</v>
+        <v>2.8584</v>
       </c>
       <c r="L2" t="n">
-        <v>1.3598</v>
+        <v>1.3779</v>
       </c>
       <c r="M2" t="n">
-        <v>0.1126</v>
+        <v>0.0054</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.586</v>
+        <v>-0.6394</v>
       </c>
       <c r="O2" t="n">
-        <v>0.6986</v>
+        <v>0.6448</v>
       </c>
       <c r="P2" t="n">
-        <v>0.8002</v>
+        <v>0.7789</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.2001</v>
+        <v>-0.1947</v>
       </c>
       <c r="R2" t="n">
-        <v>1.0003</v>
+        <v>0.9737</v>
       </c>
       <c r="S2" t="n">
-        <v>0.7537</v>
+        <v>0.1447</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.031</v>
+        <v>-0.1154</v>
       </c>
       <c r="U2" t="n">
-        <v>0.7847</v>
+        <v>0.26</v>
       </c>
       <c r="V2" t="n">
-        <v>1.6202</v>
+        <v>1.6037</v>
       </c>
       <c r="W2" t="n">
-        <v>1.1998</v>
+        <v>1.2211</v>
       </c>
       <c r="X2" t="n">
-        <v>0.4204</v>
+        <v>0.3826</v>
       </c>
     </row>
     <row r="3">
@@ -643,58 +643,58 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.8242</v>
+        <v>4.2085</v>
       </c>
       <c r="E3" t="n">
-        <v>2.5388</v>
+        <v>3.0529</v>
       </c>
       <c r="F3" t="n">
-        <v>1.2854</v>
+        <v>1.1556</v>
       </c>
       <c r="G3" t="n">
-        <v>3.5671</v>
+        <v>3.5438</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0964</v>
+        <v>0.0359</v>
       </c>
       <c r="I3" t="n">
-        <v>3.4707</v>
+        <v>3.5079</v>
       </c>
       <c r="J3" t="n">
-        <v>3.1833</v>
+        <v>3.2726</v>
       </c>
       <c r="K3" t="n">
-        <v>0.14</v>
+        <v>0.1437</v>
       </c>
       <c r="L3" t="n">
-        <v>3.0434</v>
+        <v>3.1289</v>
       </c>
       <c r="M3" t="n">
-        <v>0.3838</v>
+        <v>0.2712</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.0436</v>
+        <v>-0.1078</v>
       </c>
       <c r="O3" t="n">
-        <v>0.4274</v>
+        <v>0.379</v>
       </c>
       <c r="P3" t="n">
-        <v>0.6002</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>0.6002</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.3431</v>
+        <v>0.0805</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.6446</v>
+        <v>-0.2196</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3015</v>
+        <v>0.3002</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.9681</v>
+        <v>2.3756</v>
       </c>
       <c r="E4" t="n">
-        <v>1.1347</v>
+        <v>1.2299</v>
       </c>
       <c r="F4" t="n">
-        <v>1.8334</v>
+        <v>1.1457</v>
       </c>
       <c r="G4" t="n">
-        <v>2.4157</v>
+        <v>2.4201</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8928</v>
+        <v>0.9355</v>
       </c>
       <c r="I4" t="n">
-        <v>1.5228</v>
+        <v>1.4846</v>
       </c>
       <c r="J4" t="n">
-        <v>1.7032</v>
+        <v>1.8094</v>
       </c>
       <c r="K4" t="n">
-        <v>1.5432</v>
+        <v>1.6473</v>
       </c>
       <c r="L4" t="n">
-        <v>0.16</v>
+        <v>0.1621</v>
       </c>
       <c r="M4" t="n">
-        <v>0.7125</v>
+        <v>0.6107</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.6503</v>
+        <v>-0.7118</v>
       </c>
       <c r="O4" t="n">
-        <v>1.3629</v>
+        <v>1.3225</v>
       </c>
       <c r="P4" t="n">
-        <v>-2.6007</v>
+        <v>-2.5316</v>
       </c>
       <c r="Q4" t="n">
-        <v>-4.2012</v>
+        <v>-4.0895</v>
       </c>
       <c r="R4" t="n">
-        <v>1.6005</v>
+        <v>1.5579</v>
       </c>
       <c r="S4" t="n">
-        <v>0.7537</v>
+        <v>0.045</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0334</v>
+        <v>-0.1532</v>
       </c>
       <c r="U4" t="n">
-        <v>0.7202</v>
+        <v>0.1982</v>
       </c>
       <c r="V4" t="n">
-        <v>2.3995</v>
+        <v>2.4421</v>
       </c>
       <c r="W4" t="n">
-        <v>3.5993</v>
+        <v>3.6632</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.1998</v>
+        <v>-1.2211</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. PEREZ BENITO</t>
+          <t>M. SAINZ DE LA MAZA GARRASTACHU</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.6435</v>
+        <v>1.9601</v>
       </c>
       <c r="E5" t="n">
-        <v>2.9331</v>
+        <v>1.249</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.2895</v>
+        <v>0.7112000000000001</v>
       </c>
       <c r="G5" t="n">
-        <v>2.5793</v>
+        <v>1.6133</v>
       </c>
       <c r="H5" t="n">
-        <v>2.913</v>
+        <v>1.1627</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.3337</v>
+        <v>0.4506</v>
       </c>
       <c r="J5" t="n">
-        <v>4.0665</v>
+        <v>2.5763</v>
       </c>
       <c r="K5" t="n">
-        <v>2.821</v>
+        <v>1.1495</v>
       </c>
       <c r="L5" t="n">
-        <v>1.2455</v>
+        <v>1.4268</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.4872</v>
+        <v>-0.963</v>
       </c>
       <c r="N5" t="n">
-        <v>0.092</v>
+        <v>0.0132</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.5792</v>
+        <v>-0.9762</v>
       </c>
       <c r="P5" t="n">
-        <v>0.2001</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.2006</v>
+        <v>-2.3368</v>
       </c>
       <c r="R5" t="n">
-        <v>2.4007</v>
+        <v>2.921</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1239</v>
+        <v>-1.1274</v>
       </c>
       <c r="T5" t="n">
-        <v>1.0671</v>
+        <v>-0.491</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.9432</v>
+        <v>-0.6364</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.2598</v>
+        <v>0.89</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.5005</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.2598</v>
+        <v>-0.6105</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. SAINZ DE LA MAZA GARRASTACHU</t>
+          <t>J. PEREZ BENITO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.3074</v>
+        <v>1.9023</v>
       </c>
       <c r="E6" t="n">
-        <v>0.5109</v>
+        <v>2.0847</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7965</v>
+        <v>-0.1824</v>
       </c>
       <c r="G6" t="n">
-        <v>1.681</v>
+        <v>2.6416</v>
       </c>
       <c r="H6" t="n">
-        <v>1.2186</v>
+        <v>2.9527</v>
       </c>
       <c r="I6" t="n">
-        <v>0.4624</v>
+        <v>-0.3111</v>
       </c>
       <c r="J6" t="n">
-        <v>2.4833</v>
+        <v>4.2573</v>
       </c>
       <c r="K6" t="n">
-        <v>1.1197</v>
+        <v>2.9276</v>
       </c>
       <c r="L6" t="n">
-        <v>1.3636</v>
+        <v>1.3296</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.8023</v>
+        <v>-1.6157</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0989</v>
+        <v>0.0251</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.9012</v>
+        <v>-1.6407</v>
       </c>
       <c r="P6" t="n">
-        <v>0.6002</v>
+        <v>0.1947</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.4007</v>
+        <v>-2.1421</v>
       </c>
       <c r="R6" t="n">
-        <v>3.0009</v>
+        <v>2.3368</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.8335</v>
+        <v>-0.6546</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.0313</v>
+        <v>-0.0304</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.8022</v>
+        <v>-0.6241</v>
       </c>
       <c r="V6" t="n">
-        <v>0.8597</v>
+        <v>-0.2795</v>
       </c>
       <c r="W6" t="n">
-        <v>1.4596</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.5999</v>
+        <v>-0.2795</v>
       </c>
     </row>
     <row r="7">
@@ -955,58 +955,58 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8764</v>
+        <v>1.5461</v>
       </c>
       <c r="E7" t="n">
-        <v>1.1713</v>
+        <v>1.7605</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.2949</v>
+        <v>-0.2145</v>
       </c>
       <c r="G7" t="n">
-        <v>2.051</v>
+        <v>2.0684</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.1956</v>
+        <v>-0.1945</v>
       </c>
       <c r="I7" t="n">
-        <v>2.2465</v>
+        <v>2.2629</v>
       </c>
       <c r="J7" t="n">
-        <v>3.1451</v>
+        <v>3.2723</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.0164</v>
+        <v>0.0463</v>
       </c>
       <c r="L7" t="n">
-        <v>3.1615</v>
+        <v>3.226</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.0941</v>
+        <v>-1.2038</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.1792</v>
+        <v>-0.2407</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.9149</v>
+        <v>-0.9631</v>
       </c>
       <c r="P7" t="n">
-        <v>0.6002</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.2003</v>
+        <v>-1.1684</v>
       </c>
       <c r="R7" t="n">
-        <v>1.8005</v>
+        <v>1.7526</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.7747</v>
+        <v>-1.1066</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.7735</v>
+        <v>-0.3433</v>
       </c>
       <c r="U7" t="n">
-        <v>-1.0012</v>
+        <v>-0.7633</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.3305</v>
+        <v>0.7272999999999999</v>
       </c>
       <c r="E8" t="n">
-        <v>1.074</v>
+        <v>1.5214</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.7435</v>
+        <v>-0.7942</v>
       </c>
       <c r="G8" t="n">
-        <v>1.4866</v>
+        <v>1.4929</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.9492</v>
+        <v>-0.9303</v>
       </c>
       <c r="I8" t="n">
-        <v>2.4358</v>
+        <v>2.4232</v>
       </c>
       <c r="J8" t="n">
-        <v>1.9233</v>
+        <v>2.0126</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0436</v>
+        <v>0.1078</v>
       </c>
       <c r="L8" t="n">
-        <v>1.8797</v>
+        <v>1.9047</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.4367</v>
+        <v>-0.5197000000000001</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.9928</v>
+        <v>-1.0381</v>
       </c>
       <c r="O8" t="n">
-        <v>0.5561</v>
+        <v>0.5185</v>
       </c>
       <c r="P8" t="n">
-        <v>1.8005</v>
+        <v>1.7526</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.4001</v>
+        <v>-0.3895</v>
       </c>
       <c r="R8" t="n">
-        <v>2.2006</v>
+        <v>2.1421</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.4971</v>
+        <v>-1.0177</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.709</v>
+        <v>-0.3812</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.7881</v>
+        <v>-0.6366000000000001</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.4596</v>
+        <v>-1.5005</v>
       </c>
       <c r="W8" t="n">
-        <v>0.2598</v>
+        <v>0.2795</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.7194</v>
+        <v>-1.78</v>
       </c>
     </row>
     <row r="9">
@@ -1111,64 +1111,64 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.7777</v>
+        <v>-1.1561</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.1474</v>
+        <v>-2.5929</v>
       </c>
       <c r="F9" t="n">
-        <v>1.3697</v>
+        <v>1.4368</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.7318</v>
+        <v>-0.6840000000000001</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.6206</v>
+        <v>-0.5803</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1112</v>
+        <v>-0.1037</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.7088</v>
+        <v>-0.5565</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.0346</v>
+        <v>0.0591</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.6742</v>
+        <v>-0.6156</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.023</v>
+        <v>-0.1275</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.586</v>
+        <v>-0.6394</v>
       </c>
       <c r="O9" t="n">
-        <v>0.5629999999999999</v>
+        <v>0.5119</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.6002</v>
+        <v>-0.5842000000000001</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.2006</v>
+        <v>-2.1421</v>
       </c>
       <c r="R9" t="n">
-        <v>1.6005</v>
+        <v>1.5579</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.0456</v>
+        <v>-0.4984</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.8379</v>
+        <v>-0.5048</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2077</v>
+        <v>0.0064</v>
       </c>
       <c r="V9" t="n">
-        <v>0.5999</v>
+        <v>0.6105</v>
       </c>
       <c r="W9" t="n">
-        <v>0.5999</v>
+        <v>0.6105</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>I. SALAZAR ORTEGA</t>
+          <t>I. CHACON RODRIGUEZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.7827</v>
+        <v>-2.634</v>
       </c>
       <c r="E10" t="n">
-        <v>0.2929</v>
+        <v>-1.7283</v>
       </c>
       <c r="F10" t="n">
-        <v>-3.0756</v>
+        <v>-0.9056999999999999</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.0535</v>
+        <v>-1.0944</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.1609</v>
+        <v>-0.741</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1074</v>
+        <v>-0.3534</v>
       </c>
       <c r="J10" t="n">
-        <v>0.2911</v>
+        <v>-0.4353</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.7886</v>
+        <v>0.1642</v>
       </c>
       <c r="L10" t="n">
-        <v>2.0797</v>
+        <v>-0.5995</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.3445</v>
+        <v>-0.6591</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.3722</v>
+        <v>-0.9052</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.9723</v>
+        <v>0.2461</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.4001</v>
+        <v>-0.5842000000000001</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.2006</v>
+        <v>-0.9737</v>
       </c>
       <c r="R10" t="n">
-        <v>1.8005</v>
+        <v>0.3895</v>
       </c>
       <c r="S10" t="n">
-        <v>1.4706</v>
+        <v>-0.3964</v>
       </c>
       <c r="T10" t="n">
-        <v>1.0027</v>
+        <v>-0.3193</v>
       </c>
       <c r="U10" t="n">
-        <v>0.4679</v>
+        <v>-0.0771</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.7997</v>
+        <v>-0.5590000000000001</v>
       </c>
       <c r="W10" t="n">
-        <v>1.1998</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-2.9994</v>
+        <v>-0.5590000000000001</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>I. CHACON RODRIGUEZ</t>
+          <t>I. SALAZAR ORTEGA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.1616</v>
+        <v>-4.458</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.121</v>
+        <v>-0.4533</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.0406</v>
+        <v>-4.0047</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.0416</v>
+        <v>-2.05</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.6972</v>
+        <v>-2.1049</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.3443</v>
+        <v>0.0548</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.4761</v>
+        <v>0.4603</v>
       </c>
       <c r="K11" t="n">
-        <v>0.16</v>
+        <v>-1.647</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.6361</v>
+        <v>2.1074</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.5654</v>
+        <v>-2.5104</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.8572</v>
+        <v>-0.4578</v>
       </c>
       <c r="O11" t="n">
-        <v>0.2918</v>
+        <v>-2.0526</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.6002</v>
+        <v>-0.3895</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.0003</v>
+        <v>-2.1421</v>
       </c>
       <c r="R11" t="n">
-        <v>0.4001</v>
+        <v>1.7526</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.0003</v>
+        <v>-0.1869</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.6446</v>
+        <v>0.0074</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3557</v>
+        <v>-0.1943</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.5196</v>
+        <v>-1.8316</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.2211</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.5196</v>
+        <v>-3.0526</v>
       </c>
     </row>
     <row r="12">
@@ -1345,58 +1345,58 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.8693</v>
+        <v>-5.4703</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.8191</v>
+        <v>-3.5186</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.0502</v>
+        <v>-1.9517</v>
       </c>
       <c r="G12" t="n">
-        <v>-4.4042</v>
+        <v>-4.4364</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.313</v>
+        <v>-0.3402</v>
       </c>
       <c r="I12" t="n">
-        <v>-4.0912</v>
+        <v>-4.0961</v>
       </c>
       <c r="J12" t="n">
-        <v>-2.4321</v>
+        <v>-2.3733</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.598</v>
+        <v>-0.5824</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.834</v>
+        <v>-1.7909</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.9722</v>
+        <v>-2.0631</v>
       </c>
       <c r="N12" t="n">
-        <v>0.285</v>
+        <v>0.2422</v>
       </c>
       <c r="O12" t="n">
-        <v>-2.2572</v>
+        <v>-2.3052</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.4001</v>
+        <v>-0.3895</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.0003</v>
+        <v>-0.9737</v>
       </c>
       <c r="R12" t="n">
-        <v>0.6002</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.065</v>
+        <v>-0.6444</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.3867</v>
+        <v>-0.1717</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.6782</v>
+        <v>-0.4728</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.728099999999999</v>
+        <v>5.770399999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>5.619499999999999</v>
+        <v>7.752499999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>0.1085999999999996</v>
+        <v>-1.9822</v>
       </c>
       <c r="G13" t="n">
-        <v>9.744800000000001</v>
+        <v>9.756999999999998</v>
       </c>
       <c r="H13" t="n">
-        <v>2.321099999999999</v>
+        <v>2.4145</v>
       </c>
       <c r="I13" t="n">
-        <v>7.4236</v>
+        <v>7.3424</v>
       </c>
       <c r="J13" t="n">
-        <v>17.2614</v>
+        <v>18.532</v>
       </c>
       <c r="K13" t="n">
-        <v>6.1127</v>
+        <v>6.874499999999999</v>
       </c>
       <c r="L13" t="n">
-        <v>11.1489</v>
+        <v>11.6574</v>
       </c>
       <c r="M13" t="n">
-        <v>-7.516500000000001</v>
+        <v>-8.775</v>
       </c>
       <c r="N13" t="n">
-        <v>-3.791399999999999</v>
+        <v>-4.459699999999999</v>
       </c>
       <c r="O13" t="n">
-        <v>-3.725</v>
+        <v>-4.315</v>
       </c>
       <c r="P13" t="n">
-        <v>9.99999999995449e-05</v>
+        <v>-0.000200000000000089</v>
       </c>
       <c r="Q13" t="n">
-        <v>-17.0048</v>
+        <v>-16.5526</v>
       </c>
       <c r="R13" t="n">
-        <v>17.005</v>
+        <v>16.5525</v>
       </c>
       <c r="S13" t="n">
-        <v>-5.4574</v>
+        <v>-5.3622</v>
       </c>
       <c r="T13" t="n">
-        <v>-2.9554</v>
+        <v>-2.7225</v>
       </c>
       <c r="U13" t="n">
-        <v>-2.502</v>
+        <v>-2.6398</v>
       </c>
       <c r="V13" t="n">
-        <v>1.4406</v>
+        <v>1.3757</v>
       </c>
       <c r="W13" t="n">
-        <v>8.318200000000001</v>
+        <v>8.495899999999999</v>
       </c>
       <c r="X13" t="n">
-        <v>-6.8775</v>
+        <v>-7.1201</v>
       </c>
     </row>
     <row r="14">
@@ -1501,64 +1501,64 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>6.6782</v>
+        <v>5.0176</v>
       </c>
       <c r="E14" t="n">
-        <v>4.3864</v>
+        <v>3.8578</v>
       </c>
       <c r="F14" t="n">
-        <v>2.2918</v>
+        <v>1.1598</v>
       </c>
       <c r="G14" t="n">
-        <v>4.0492</v>
+        <v>4.0475</v>
       </c>
       <c r="H14" t="n">
-        <v>1.782</v>
+        <v>1.8042</v>
       </c>
       <c r="I14" t="n">
-        <v>2.2671</v>
+        <v>2.2432</v>
       </c>
       <c r="J14" t="n">
-        <v>5.1225</v>
+        <v>5.2868</v>
       </c>
       <c r="K14" t="n">
-        <v>2.4829</v>
+        <v>2.6121</v>
       </c>
       <c r="L14" t="n">
-        <v>2.6396</v>
+        <v>2.6747</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.0734</v>
+        <v>-1.2393</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.7009</v>
+        <v>-0.8078</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.3725</v>
+        <v>-0.4315</v>
       </c>
       <c r="P14" t="n">
-        <v>-1.0003</v>
+        <v>-0.9737</v>
       </c>
       <c r="Q14" t="n">
-        <v>-2.4007</v>
+        <v>-2.3368</v>
       </c>
       <c r="R14" t="n">
-        <v>1.4004</v>
+        <v>1.3632</v>
       </c>
       <c r="S14" t="n">
-        <v>3.1097</v>
+        <v>1.3848</v>
       </c>
       <c r="T14" t="n">
-        <v>1.145</v>
+        <v>0.3489</v>
       </c>
       <c r="U14" t="n">
-        <v>1.9647</v>
+        <v>1.036</v>
       </c>
       <c r="V14" t="n">
-        <v>0.5196</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="W14" t="n">
-        <v>0.5196</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="X14" t="n">
         <v>0</v>
@@ -1579,64 +1579,64 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.3841</v>
+        <v>4.542</v>
       </c>
       <c r="E15" t="n">
-        <v>3.8125</v>
+        <v>4.9713</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.4284</v>
+        <v>-0.4293</v>
       </c>
       <c r="G15" t="n">
-        <v>0.1427</v>
+        <v>0.2651</v>
       </c>
       <c r="H15" t="n">
-        <v>0.2581</v>
+        <v>0.2335</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.1154</v>
+        <v>0.0316</v>
       </c>
       <c r="J15" t="n">
-        <v>3.6801</v>
+        <v>4.0083</v>
       </c>
       <c r="K15" t="n">
-        <v>1.0233</v>
+        <v>1.1136</v>
       </c>
       <c r="L15" t="n">
-        <v>2.6568</v>
+        <v>2.8947</v>
       </c>
       <c r="M15" t="n">
-        <v>-3.5374</v>
+        <v>-3.7433</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.7652</v>
+        <v>-0.8802</v>
       </c>
       <c r="O15" t="n">
-        <v>-2.7722</v>
+        <v>-2.8631</v>
       </c>
       <c r="P15" t="n">
-        <v>1.6005</v>
+        <v>1.5579</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.6005</v>
+        <v>-1.5579</v>
       </c>
       <c r="R15" t="n">
-        <v>3.2009</v>
+        <v>3.1158</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.4185</v>
+        <v>0.608</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.3266</v>
+        <v>0.4098</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.0919</v>
+        <v>0.1982</v>
       </c>
       <c r="V15" t="n">
-        <v>2.0594</v>
+        <v>2.1111</v>
       </c>
       <c r="W15" t="n">
-        <v>2.0594</v>
+        <v>2.1111</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.985</v>
+        <v>1.169</v>
       </c>
       <c r="E16" t="n">
-        <v>0.9367</v>
+        <v>1.4431</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0482</v>
+        <v>-0.274</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.7382</v>
+        <v>-0.7103</v>
       </c>
       <c r="H16" t="n">
-        <v>2.4957</v>
+        <v>2.499</v>
       </c>
       <c r="I16" t="n">
-        <v>-3.2338</v>
+        <v>-3.2093</v>
       </c>
       <c r="J16" t="n">
-        <v>0.8707</v>
+        <v>1.0725</v>
       </c>
       <c r="K16" t="n">
-        <v>3.4608</v>
+        <v>3.5845</v>
       </c>
       <c r="L16" t="n">
-        <v>-2.5901</v>
+        <v>-2.512</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.6089</v>
+        <v>-1.7827</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.9651</v>
+        <v>-1.0854</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.6437</v>
+        <v>-0.6973</v>
       </c>
       <c r="P16" t="n">
-        <v>0.8002</v>
+        <v>0.7789</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.6005</v>
+        <v>-1.5579</v>
       </c>
       <c r="R16" t="n">
-        <v>2.4007</v>
+        <v>2.3368</v>
       </c>
       <c r="S16" t="n">
-        <v>0.323</v>
+        <v>0.4898</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.1332</v>
+        <v>0.0969</v>
       </c>
       <c r="U16" t="n">
-        <v>0.4562</v>
+        <v>0.3929</v>
       </c>
       <c r="V16" t="n">
-        <v>0.5999</v>
+        <v>0.6105</v>
       </c>
       <c r="W16" t="n">
-        <v>1.7997</v>
+        <v>1.8316</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.1998</v>
+        <v>-1.2211</v>
       </c>
     </row>
     <row r="17">
@@ -1735,64 +1735,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.235</v>
+        <v>-0.7741</v>
       </c>
       <c r="E17" t="n">
-        <v>0.4283</v>
+        <v>-0.007</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.6633</v>
+        <v>-0.7671</v>
       </c>
       <c r="G17" t="n">
-        <v>-2.3865</v>
+        <v>-2.4066</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.2248</v>
+        <v>-1.2069</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.1617</v>
+        <v>-1.1997</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.5362</v>
+        <v>-0.4895</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.6962</v>
+        <v>-0.6516</v>
       </c>
       <c r="L17" t="n">
-        <v>0.16</v>
+        <v>0.1621</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.8503</v>
+        <v>-1.9171</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.5286</v>
+        <v>-0.5553</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.3217</v>
+        <v>-1.3618</v>
       </c>
       <c r="P17" t="n">
-        <v>0.8002</v>
+        <v>0.7789</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.2001</v>
+        <v>-0.1947</v>
       </c>
       <c r="R17" t="n">
-        <v>1.0003</v>
+        <v>0.9737</v>
       </c>
       <c r="S17" t="n">
-        <v>1.0915</v>
+        <v>0.5741000000000001</v>
       </c>
       <c r="T17" t="n">
-        <v>0.9048</v>
+        <v>0.3978</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1867</v>
+        <v>0.1763</v>
       </c>
       <c r="V17" t="n">
-        <v>0.2598</v>
+        <v>0.2795</v>
       </c>
       <c r="W17" t="n">
-        <v>0.2598</v>
+        <v>0.2795</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. PAZ CACHEIRO</t>
+          <t>A. CARDITO MARTIN</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.3067</v>
+        <v>-0.9873</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.8637</v>
+        <v>-0.7738</v>
       </c>
       <c r="F18" t="n">
-        <v>0.5570000000000001</v>
+        <v>-0.2135</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.3149</v>
+        <v>0.4601</v>
       </c>
       <c r="H18" t="n">
-        <v>0.06950000000000001</v>
+        <v>-0.7313</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.3843</v>
+        <v>1.1913</v>
       </c>
       <c r="J18" t="n">
-        <v>0.0437</v>
+        <v>1.3784</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0418</v>
+        <v>0.0411</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0019</v>
+        <v>1.3374</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.3586</v>
+        <v>-0.9184</v>
       </c>
       <c r="N18" t="n">
-        <v>0.0277</v>
+        <v>-0.7723</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.3862</v>
+        <v>-0.146</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.6005</v>
+        <v>-2.1421</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.6007</v>
+        <v>-2.5316</v>
       </c>
       <c r="R18" t="n">
-        <v>1.0003</v>
+        <v>0.3895</v>
       </c>
       <c r="S18" t="n">
-        <v>1.7692</v>
+        <v>0.6947</v>
       </c>
       <c r="T18" t="n">
-        <v>1.854</v>
+        <v>0.3793</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0848</v>
+        <v>0.3154</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.1606</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.1606</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. CARDITO MARTIN</t>
+          <t>M. PAZ CACHEIRO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.3618</v>
+        <v>-1.1956</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.1631</v>
+        <v>-1.8058</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.1987</v>
+        <v>0.6102</v>
       </c>
       <c r="G19" t="n">
-        <v>0.5163</v>
+        <v>-0.3668</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.6816</v>
+        <v>0.0271</v>
       </c>
       <c r="I19" t="n">
-        <v>1.1979</v>
+        <v>-0.3939</v>
       </c>
       <c r="J19" t="n">
-        <v>1.3598</v>
+        <v>0.0989</v>
       </c>
       <c r="K19" t="n">
-        <v>0.04</v>
+        <v>0.07439999999999999</v>
       </c>
       <c r="L19" t="n">
-        <v>1.3198</v>
+        <v>0.0244</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.8435</v>
+        <v>-0.4657</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.7216</v>
+        <v>-0.0473</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.1219</v>
+        <v>-0.4184</v>
       </c>
       <c r="P19" t="n">
-        <v>-2.2006</v>
+        <v>-1.5579</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.6007</v>
+        <v>-2.5316</v>
       </c>
       <c r="R19" t="n">
-        <v>0.4001</v>
+        <v>0.9737</v>
       </c>
       <c r="S19" t="n">
-        <v>0.3225</v>
+        <v>0.8322000000000001</v>
       </c>
       <c r="T19" t="n">
-        <v>0.07779999999999999</v>
+        <v>0.73</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2447</v>
+        <v>0.1022</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>-0.1032</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>-0.1032</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.2335</v>
+        <v>-1.6519</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.4544</v>
+        <v>-0.8638</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.7791</v>
+        <v>-0.7882</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.6602</v>
+        <v>-2.6556</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.4468</v>
+        <v>-0.4398</v>
       </c>
       <c r="I20" t="n">
-        <v>-2.2134</v>
+        <v>-2.2158</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.8743</v>
+        <v>-0.8056</v>
       </c>
       <c r="K20" t="n">
-        <v>0.2817</v>
+        <v>0.3208</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.156</v>
+        <v>-1.1264</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.7859</v>
+        <v>-1.85</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.7285</v>
+        <v>-0.7605</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.0574</v>
+        <v>-1.0895</v>
       </c>
       <c r="P20" t="n">
-        <v>1.8005</v>
+        <v>1.7526</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.8005</v>
+        <v>1.7526</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.774</v>
+        <v>-0.1384</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.5800999999999999</v>
+        <v>-0.0581</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1939</v>
+        <v>-0.0803</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.5999</v>
+        <v>-0.6105</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.5999</v>
+        <v>-0.6105</v>
       </c>
     </row>
     <row r="21">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.9371</v>
+        <v>-2.514</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.7506</v>
+        <v>-0.998</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.1865</v>
+        <v>-1.516</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.8063</v>
+        <v>-1.8434</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.1858</v>
+        <v>-1.2552</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.6205000000000001</v>
+        <v>-0.5881999999999999</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.5904</v>
+        <v>-0.4831</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.4781</v>
+        <v>-0.4592</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.1124</v>
+        <v>-0.0238</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.2159</v>
+        <v>-1.3604</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.7078</v>
+        <v>-0.796</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.5081</v>
+        <v>-0.5644</v>
       </c>
       <c r="P21" t="n">
-        <v>0.4001</v>
+        <v>0.3895</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.4001</v>
+        <v>-0.3895</v>
       </c>
       <c r="R21" t="n">
-        <v>0.8002</v>
+        <v>0.7789</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.07140000000000001</v>
+        <v>0.4405</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.7601</v>
+        <v>-0.1255</v>
       </c>
       <c r="U21" t="n">
-        <v>0.6887</v>
+        <v>0.5659999999999999</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.4596</v>
+        <v>-1.5005</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.4596</v>
+        <v>-1.5005</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>D. HOGAN</t>
+          <t>M. SOUTO PARRADO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.7265</v>
+        <v>-3.9292</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.1348</v>
+        <v>-2.4661</v>
       </c>
       <c r="F22" t="n">
-        <v>-3.5916</v>
+        <v>-1.463</v>
       </c>
       <c r="G22" t="n">
-        <v>-3.495</v>
+        <v>-2.9949</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.1197</v>
+        <v>-2.1957</v>
       </c>
       <c r="I22" t="n">
-        <v>-2.3753</v>
+        <v>-0.7992</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.116</v>
+        <v>-0.2069</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.598</v>
+        <v>-1.5931</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.518</v>
+        <v>1.3863</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.3789</v>
+        <v>-2.788</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.5217000000000001</v>
+        <v>-0.6025</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.8573</v>
+        <v>-2.1855</v>
       </c>
       <c r="P22" t="n">
-        <v>-1.4004</v>
+        <v>0.7789</v>
       </c>
       <c r="Q22" t="n">
-        <v>-3.401</v>
+        <v>-2.1421</v>
       </c>
       <c r="R22" t="n">
-        <v>2.0006</v>
+        <v>2.921</v>
       </c>
       <c r="S22" t="n">
-        <v>1.3687</v>
+        <v>-0.2127</v>
       </c>
       <c r="T22" t="n">
-        <v>0.9826</v>
+        <v>-0.1172</v>
       </c>
       <c r="U22" t="n">
-        <v>0.386</v>
+        <v>-0.0955</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.1998</v>
+        <v>-1.5005</v>
       </c>
       <c r="W22" t="n">
-        <v>2.3995</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-3.5993</v>
+        <v>-1.5005</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>M. SOUTO PARRADO</t>
+          <t>D. HOGAN</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.9747</v>
+        <v>-5.4469</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.3061</v>
+        <v>-1.3754</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.6686</v>
+        <v>-4.0714</v>
       </c>
       <c r="G23" t="n">
-        <v>-3.052</v>
+        <v>-3.5519</v>
       </c>
       <c r="H23" t="n">
-        <v>-2.2678</v>
+        <v>-1.1495</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.7843</v>
+        <v>-2.4024</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.4432</v>
+        <v>-1.0848</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.7668</v>
+        <v>-0.5824</v>
       </c>
       <c r="L23" t="n">
-        <v>1.3236</v>
+        <v>-0.5024</v>
       </c>
       <c r="M23" t="n">
-        <v>-2.6088</v>
+        <v>-2.4671</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.5009</v>
+        <v>-0.5671</v>
       </c>
       <c r="O23" t="n">
-        <v>-2.1079</v>
+        <v>-1.9</v>
       </c>
       <c r="P23" t="n">
-        <v>0.8002</v>
+        <v>-1.3632</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.2006</v>
+        <v>-3.3105</v>
       </c>
       <c r="R23" t="n">
-        <v>3.0009</v>
+        <v>1.9474</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.2634</v>
+        <v>0.6892</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.6622</v>
+        <v>0.5778</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.6011</v>
+        <v>0.1114</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.4596</v>
+        <v>-1.2211</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>2.4421</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.4596</v>
+        <v>-3.6632</v>
       </c>
     </row>
     <row r="24">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.728</v>
+        <v>-5.7704</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.1087999999999996</v>
+        <v>1.9823</v>
       </c>
       <c r="F24" t="n">
-        <v>-5.619200000000001</v>
+        <v>-7.7525</v>
       </c>
       <c r="G24" t="n">
-        <v>-9.744900000000001</v>
+        <v>-9.7568</v>
       </c>
       <c r="H24" t="n">
-        <v>-2.3212</v>
+        <v>-2.4146</v>
       </c>
       <c r="I24" t="n">
-        <v>-7.4237</v>
+        <v>-7.3424</v>
       </c>
       <c r="J24" t="n">
-        <v>7.516700000000001</v>
+        <v>8.775000000000002</v>
       </c>
       <c r="K24" t="n">
-        <v>3.791399999999999</v>
+        <v>4.4602</v>
       </c>
       <c r="L24" t="n">
-        <v>3.7252</v>
+        <v>4.315</v>
       </c>
       <c r="M24" t="n">
-        <v>-17.2616</v>
+        <v>-18.532</v>
       </c>
       <c r="N24" t="n">
-        <v>-6.1126</v>
+        <v>-6.8744</v>
       </c>
       <c r="O24" t="n">
-        <v>-11.1489</v>
+        <v>-11.6575</v>
       </c>
       <c r="P24" t="n">
-        <v>-9.999999999976694e-05</v>
+        <v>-0.0001999999999995339</v>
       </c>
       <c r="Q24" t="n">
-        <v>-17.0049</v>
+        <v>-16.5526</v>
       </c>
       <c r="R24" t="n">
-        <v>17.0049</v>
+        <v>16.5526</v>
       </c>
       <c r="S24" t="n">
-        <v>5.457300000000001</v>
+        <v>5.3622</v>
       </c>
       <c r="T24" t="n">
-        <v>2.502000000000001</v>
+        <v>2.6397</v>
       </c>
       <c r="U24" t="n">
-        <v>2.9553</v>
+        <v>2.7226</v>
       </c>
       <c r="V24" t="n">
-        <v>-1.4408</v>
+        <v>-1.3757</v>
       </c>
       <c r="W24" t="n">
-        <v>6.877400000000002</v>
+        <v>7.1201</v>
       </c>
       <c r="X24" t="n">
-        <v>-8.318199999999999</v>
+        <v>-8.495799999999999</v>
       </c>
     </row>
   </sheetData>
